--- a/calibration/phase2_bayesian_regression/renter_group/RL/RL_prob_metrics.xlsx
+++ b/calibration/phase2_bayesian_regression/renter_group/RL/RL_prob_metrics.xlsx
@@ -112,25 +112,43 @@
     <t>none</t>
   </si>
   <si>
-    <t>temp</t>
-  </si>
-  <si>
-    <t>{'tau': 1.6}</t>
-  </si>
-  <si>
-    <t>{'tau': 0.8250000000000001}</t>
-  </si>
-  <si>
-    <t>[0.5313892  0.52042955 0.5408976  0.30723968 0.42017964 0.49159786
- 0.45831653 0.48258245 0.36568397 0.5247864  0.52290505 0.5592613
- 0.4266593  0.47618705 0.5186112  0.45787036 0.47260106 0.47408727
- 0.60384154 0.59398335 0.31020674 0.48082978]</t>
-  </si>
-  <si>
-    <t>[0.45449647 0.38304278 0.2544885  0.36846069 0.25232035 0.6334702
- 0.44224736 0.4130815  0.6186332  0.6783257  0.5739521  0.67792374
- 0.5577969  0.4983204  0.21939903 0.48319304 0.622822   0.55537355
- 0.38781545 0.65487015 0.18253301 0.45719847 0.38843232]</t>
+    <t>platt</t>
+  </si>
+  <si>
+    <t>{'coef': -0.41106453249314256, 'intercept': -0.24175168855314116, 'C': 0.2}</t>
+  </si>
+  <si>
+    <t>{'coef': 0.6472996770141207, 'intercept': -0.33269705335365346, 'C': 0.2}</t>
+  </si>
+  <si>
+    <t>[0.47028464 0.42566991 0.41098332 0.42959647 0.55781794 0.44815397
+ 0.39995726 0.47278058 0.42252497 0.35701144 0.36800567 0.3799279
+ 0.43364404 0.36079482 0.48989704 0.4763075  0.41984543 0.39954685
+ 0.55272984 0.46552172 0.37522819 0.44899391 0.35998643 0.47335149
+ 0.39009027 0.3894935  0.37160206 0.46205701 0.39552872 0.54280897
+ 0.45059081 0.42678781 0.36702694 0.42874642 0.42631283 0.42355965
+ 0.50875091 0.45338289 0.45171711 0.42227456 0.495726   0.37991864
+ 0.44621345 0.32548513 0.38777294 0.39308614 0.50380807 0.40944042
+ 0.49821135 0.41174977 0.40765627 0.38424437 0.39175026 0.38777294
+ 0.38818178 0.40539987 0.48087844 0.49892576 0.33973987 0.39319833
+ 0.43073081 0.45959529 0.48579053 0.38382934 0.4216438  0.42017605
+ 0.40195982 0.42329812 0.39279362 0.38450508 0.4757358  0.46990205
+ 0.38491569 0.42697752 0.40121585]</t>
+  </si>
+  <si>
+    <t>[0.43552312 0.49005336 0.4699346  0.31225768 0.4569001  0.32897365
+ 0.46438953 0.45651612 0.5661143  0.38964668 0.3803096  0.42689753
+ 0.3501017  0.35217202 0.3396146  0.32567528 0.3661655  0.54032594
+ 0.48113015 0.38846457 0.3940833  0.3874951  0.42445928 0.4938362
+ 0.43725693 0.32011592 0.46850052 0.44284868 0.38275    0.4985852
+ 0.5258297  0.50618255 0.4331347  0.3233373  0.44845197 0.48372433
+ 0.43244812 0.39274576 0.53132206 0.33516455 0.5545932  0.41031092
+ 0.3799907  0.5805139  0.5618351  0.32053843 0.3692582  0.4562533
+ 0.441634   0.5045052  0.49956498 0.4606156  0.4403429  0.53097236
+ 0.29083544 0.44680303 0.49765304 0.61511785 0.43543535 0.4001534
+ 0.3974716  0.28623068 0.41304013 0.49490663 0.51689255 0.43861204
+ 0.45267224 0.37039447 0.523306   0.5214405  0.29583144 0.4071488
+ 0.34192756 0.4050431  0.34048823 0.25675595 0.5365142 ]</t>
   </si>
 </sst>
 </file>
@@ -570,49 +588,49 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>0.4266666666666667</v>
       </c>
       <c r="C2">
-        <v>0.2569035291671753</v>
+        <v>0.2940920889377594</v>
       </c>
       <c r="D2">
-        <v>0.25</v>
+        <v>0.2446222222222222</v>
       </c>
       <c r="E2">
-        <v>-0.02761411666870117</v>
+        <v>-0.2022296513625703</v>
       </c>
       <c r="F2">
-        <v>0.7113697510448744</v>
+        <v>0.7851971505901416</v>
       </c>
       <c r="G2">
-        <v>0.1283650540492751</v>
+        <v>0.2053658982117971</v>
       </c>
       <c r="H2">
-        <v>0.4250945697228113</v>
+        <v>0.4258496839067211</v>
       </c>
       <c r="I2">
-        <v>0.04064715672037236</v>
+        <v>0.07661349583849296</v>
       </c>
       <c r="J2">
-        <v>0.02813852813852813</v>
+        <v>0.02534513457556936</v>
       </c>
       <c r="K2">
-        <v>0.25</v>
+        <v>0.2446222222222222</v>
       </c>
       <c r="L2">
-        <v>0.5619834710743802</v>
+        <v>0.3597383720930233</v>
       </c>
       <c r="M2">
-        <v>0.6172258297258297</v>
+        <v>0.4008755684885574</v>
       </c>
       <c r="N2">
-        <v>0.2355337291955948</v>
+        <v>0.2355819493532181</v>
       </c>
       <c r="O2">
-        <v>0.1161400005221367</v>
+        <v>0.1153477132320404</v>
       </c>
       <c r="P2">
         <v>10</v>
@@ -635,49 +653,49 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
+        <v>0.4266666666666667</v>
       </c>
       <c r="C3">
-        <v>0.251611590385437</v>
+        <v>0.2366443711278126</v>
       </c>
       <c r="D3">
-        <v>0.25</v>
+        <v>0.2446222222222222</v>
       </c>
       <c r="E3">
-        <v>-0.006446361541748047</v>
+        <v>0.0326129450625392</v>
       </c>
       <c r="F3">
-        <v>0.6972018472714265</v>
+        <v>0.6662423931351713</v>
       </c>
       <c r="G3">
-        <v>0.1075546687299555</v>
+        <v>0.05948356541012931</v>
       </c>
       <c r="H3">
-        <v>0.3961584568023682</v>
+        <v>0.266816853816028</v>
       </c>
       <c r="I3">
-        <v>0.02522188001157277</v>
+        <v>0.007453724884403291</v>
       </c>
       <c r="J3">
-        <v>0.01969696969696969</v>
+        <v>0.01625816824576515</v>
       </c>
       <c r="K3">
-        <v>0.25</v>
+        <v>0.2446222222222222</v>
       </c>
       <c r="L3">
-        <v>0.5619834710743802</v>
+        <v>0.6402616279069768</v>
       </c>
       <c r="M3">
-        <v>0.6172258297258297</v>
+        <v>0.5945702677152118</v>
       </c>
       <c r="N3">
-        <v>0.2437772303819656</v>
+        <v>0.2422539496107458</v>
       </c>
       <c r="O3">
-        <v>0.07606472074985504</v>
+        <v>0.04869544719534327</v>
       </c>
       <c r="P3">
         <v>10</v>
@@ -706,49 +724,49 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="B4">
-        <v>0.391304347826087</v>
+        <v>0.4805194805194805</v>
       </c>
       <c r="C4">
-        <v>0.1983901262283325</v>
+        <v>0.2399329841136932</v>
       </c>
       <c r="D4">
-        <v>0.2381852551984877</v>
+        <v>0.2496205093607691</v>
       </c>
       <c r="E4">
-        <v>0.1670763748032708</v>
+        <v>0.03880901161480588</v>
       </c>
       <c r="F4">
-        <v>0.5843864775173472</v>
+        <v>0.6726690893080599</v>
       </c>
       <c r="G4">
-        <v>0.1556329766045446</v>
+        <v>0.06946747411381116</v>
       </c>
       <c r="H4">
-        <v>0.3906616866588593</v>
+        <v>0.3897486726442972</v>
       </c>
       <c r="I4">
-        <v>0.04249449229655916</v>
+        <v>0.01321729744330852</v>
       </c>
       <c r="J4">
-        <v>0.07417559336273892</v>
+        <v>0.0223191120058958</v>
       </c>
       <c r="K4">
-        <v>0.2381852551984877</v>
+        <v>0.2496205093607691</v>
       </c>
       <c r="L4">
-        <v>0.8174603174603174</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="M4">
-        <v>0.7785893119226452</v>
+        <v>0.6259235309399658</v>
       </c>
       <c r="N4">
-        <v>0.2338529825210571</v>
+        <v>0.2352633029222488</v>
       </c>
       <c r="O4">
-        <v>0.1239850074052811</v>
+        <v>0.1201512441039085</v>
       </c>
       <c r="P4">
         <v>10</v>
@@ -771,49 +789,49 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="B5">
-        <v>0.391304347826087</v>
+        <v>0.4805194805194805</v>
       </c>
       <c r="C5">
-        <v>0.1925484389066696</v>
+        <v>0.2413518130779266</v>
       </c>
       <c r="D5">
-        <v>0.2381852551984877</v>
+        <v>0.2496205093607691</v>
       </c>
       <c r="E5">
-        <v>0.1916021890346967</v>
+        <v>0.03312506774390056</v>
       </c>
       <c r="F5">
-        <v>0.5697011042393206</v>
+        <v>0.6759877838332202</v>
       </c>
       <c r="G5">
-        <v>0.1951753231494323</v>
+        <v>0.064925251069007</v>
       </c>
       <c r="H5">
-        <v>0.3819378018379211</v>
+        <v>0.3848821520805359</v>
       </c>
       <c r="I5">
-        <v>0.0527472501814145</v>
+        <v>0.007703804070528019</v>
       </c>
       <c r="J5">
-        <v>0.09325771896660363</v>
+        <v>0.01523584640467758</v>
       </c>
       <c r="K5">
-        <v>0.2381852551984877</v>
+        <v>0.2496205093607691</v>
       </c>
       <c r="L5">
-        <v>0.8174603174603174</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="M5">
-        <v>0.7785893119226452</v>
+        <v>0.6259235309399658</v>
       </c>
       <c r="N5">
-        <v>0.2274553924798965</v>
+        <v>0.2390951216220856</v>
       </c>
       <c r="O5">
-        <v>0.1466438174247742</v>
+        <v>0.07829184085130692</v>
       </c>
       <c r="P5">
         <v>10</v>
